--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92561917413</v>
+        <v>46157.93070772146</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93070772146</v>
+        <v>46157.93153152123</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93153152123</v>
+        <v>46157.93393627187</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93393627187</v>
+        <v>46157.93708195783</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93708195783</v>
+        <v>46158.28210625276</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28210625276</v>
+        <v>46158.29665694986</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29665694986</v>
+        <v>46158.29805074671</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29805074671</v>
+        <v>46158.33381348075</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33381348075</v>
+        <v>46158.36847887192</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Кореньков/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Кореньков/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36847887192</v>
+        <v>46158.37281560207</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
